--- a/data/raw/김포 25년/항공통계상세조회(노선) (8).xlsx
+++ b/data/raw/김포 25년/항공통계상세조회(노선) (8).xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="72">
   <si>
     <t>SEQ</t>
   </si>
@@ -38,13 +38,13 @@
     <t/>
   </si>
   <si>
-    <t>10794</t>
-  </si>
-  <si>
-    <t>1980465</t>
-  </si>
-  <si>
-    <t>15603</t>
+    <t>5405</t>
+  </si>
+  <si>
+    <t>981959</t>
+  </si>
+  <si>
+    <t>7651</t>
   </si>
   <si>
     <t>김포(GMP)</t>
@@ -53,184 +53,181 @@
     <t>간사이(KIX)</t>
   </si>
   <si>
-    <t>413</t>
-  </si>
-  <si>
-    <t>70118</t>
-  </si>
-  <si>
-    <t>669</t>
+    <t>207</t>
+  </si>
+  <si>
+    <t>33302</t>
+  </si>
+  <si>
+    <t>321</t>
   </si>
   <si>
     <t>광주(KWJ)</t>
   </si>
   <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>6209</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>김해(PUS)</t>
+  </si>
+  <si>
+    <t>582</t>
+  </si>
+  <si>
+    <t>89313</t>
+  </si>
+  <si>
+    <t>344</t>
+  </si>
+  <si>
+    <t>나고야(NGO)</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>5691</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>다싱(PKX)</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>5546</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>대구(TAE)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>도쿄 하네다(HND)</t>
+  </si>
+  <si>
+    <t>372</t>
+  </si>
+  <si>
+    <t>81559</t>
+  </si>
+  <si>
+    <t>1370</t>
+  </si>
+  <si>
+    <t>북경(PEK)</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>10718</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>사천(HIN)</t>
+  </si>
+  <si>
+    <t>7020</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>쑹산(TSA)</t>
+  </si>
+  <si>
+    <t>10271</t>
+  </si>
+  <si>
+    <t>여수(RSU)</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>9574</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>울산(USN)</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>10606</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>제주(CJU)</t>
+  </si>
+  <si>
+    <t>3526</t>
+  </si>
+  <si>
+    <t>672487</t>
+  </si>
+  <si>
+    <t>4635</t>
+  </si>
+  <si>
+    <t>카오슝(KHH)</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>8483</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>포항 경주(KPO)</t>
+  </si>
+  <si>
+    <t>2363</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>홍차오(SHA)</t>
+  </si>
+  <si>
     <t>124</t>
   </si>
   <si>
-    <t>12919</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>김해(PUS)</t>
-  </si>
-  <si>
-    <t>1161</t>
-  </si>
-  <si>
-    <t>177019</t>
-  </si>
-  <si>
-    <t>685</t>
-  </si>
-  <si>
-    <t>나고야(NGO)</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>12029</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>다싱(PKX)</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>11508</t>
-  </si>
-  <si>
-    <t>155</t>
-  </si>
-  <si>
-    <t>대구(TAE)</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>도쿄 하네다(HND)</t>
-  </si>
-  <si>
-    <t>744</t>
-  </si>
-  <si>
-    <t>163287</t>
-  </si>
-  <si>
-    <t>2280</t>
-  </si>
-  <si>
-    <t>북경(PEK)</t>
-  </si>
-  <si>
-    <t>154</t>
-  </si>
-  <si>
-    <t>22791</t>
-  </si>
-  <si>
-    <t>268</t>
-  </si>
-  <si>
-    <t>사천(HIN)</t>
-  </si>
-  <si>
-    <t>14320</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>쑹산(TSA)</t>
-  </si>
-  <si>
-    <t>20569</t>
-  </si>
-  <si>
-    <t>237</t>
-  </si>
-  <si>
-    <t>여수(RSU)</t>
-  </si>
-  <si>
-    <t>176</t>
-  </si>
-  <si>
-    <t>20001</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>울산(USN)</t>
-  </si>
-  <si>
-    <t>182</t>
-  </si>
-  <si>
-    <t>21847</t>
-  </si>
-  <si>
-    <t>제주(CJU)</t>
-  </si>
-  <si>
-    <t>7042</t>
-  </si>
-  <si>
-    <t>1352982</t>
-  </si>
-  <si>
-    <t>9862</t>
-  </si>
-  <si>
-    <t>카오슝(KHH)</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>17272</t>
-  </si>
-  <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>포항 경주(KPO)</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>4609</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>홍차오(SHA)</t>
-  </si>
-  <si>
-    <t>248</t>
-  </si>
-  <si>
-    <t>59062</t>
-  </si>
-  <si>
-    <t>936</t>
+    <t>28685</t>
+  </si>
+  <si>
+    <t>363</t>
   </si>
 </sst>
 </file>
@@ -521,7 +518,7 @@
         <v>48</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -532,16 +529,16 @@
         <v>11</v>
       </c>
       <c r="C13" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="D13" t="s" s="0">
+      <c r="E13" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="E13" t="s" s="0">
+      <c r="F13" t="s" s="0">
         <v>52</v>
-      </c>
-      <c r="F13" t="s" s="0">
-        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -552,16 +549,16 @@
         <v>11</v>
       </c>
       <c r="C14" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="D14" t="s" s="0">
         <v>54</v>
       </c>
-      <c r="D14" t="s" s="0">
+      <c r="E14" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="E14" t="s" s="0">
+      <c r="F14" t="s" s="0">
         <v>56</v>
-      </c>
-      <c r="F14" t="s" s="0">
-        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -615,13 +612,13 @@
         <v>65</v>
       </c>
       <c r="D17" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="E17" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="E17" t="s" s="0">
+      <c r="F17" t="s" s="0">
         <v>67</v>
-      </c>
-      <c r="F17" t="s" s="0">
-        <v>68</v>
       </c>
     </row>
     <row r="18">
@@ -632,16 +629,16 @@
         <v>11</v>
       </c>
       <c r="C18" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D18" t="s" s="0">
+      <c r="E18" t="s" s="0">
         <v>70</v>
       </c>
-      <c r="E18" t="s" s="0">
+      <c r="F18" t="s" s="0">
         <v>71</v>
-      </c>
-      <c r="F18" t="s" s="0">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
